--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_システムとの突合_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_システムとの突合_20260928.xlsx
@@ -12,8 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_差の分解" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_前提の対比" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_保険料の内訳" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_当方の算式の訂正" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_残っている作業" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_残っている作業" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,25 +113,22 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -512,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -603,12 +599,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>【要訂正】当方の算式の誤りが1件。調整交付金見込額の基数に総合事業費を含めていなかった</t>
+          <t>当方の算定6,048円との差+485円。うち480円が標準給付費の差</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>要訂正</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -618,12 +614,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>→ 当方の算定は6,095円ではなく6,048円（▲47円）。100円未満切上げの6,100円は不変</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>地域支援事業費は1円まで一致</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -633,12 +629,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>当方の算定6,048円との差+485円。うち480円が標準給付費の差</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>補正後被保険者数 10,234.69人を当方の標準割合で再現（小数2位まで一致）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -648,40 +644,10 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>地域支援事業費は1円まで一致</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>補正後被保険者数 10,234.69人を当方の標準割合で再現（小数2位まで一致）</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
           <t>切上げるとシステム6,600円（第9期と同額）、当方6,100円（▲500円）</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -891,7 +857,7 @@
           <t>33件</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1055,16 +1021,16 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>当方の算定（訂正後）</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
+          <t>当方の算定</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>6047.771219371468</v>
       </c>
-      <c r="C2" s="8" t="n"/>
+      <c r="C2" s="7" t="n"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>本書の第2章のとおり訂正した値</t>
+          <t>本業務による算定</t>
         </is>
       </c>
     </row>
@@ -1074,10 +1040,10 @@
           <t xml:space="preserve">　予定保険料収納率を99.35％→99.40％に</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="6" t="n">
         <v>6044.729080931141</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="7" t="n">
         <v>-3.042138440327108</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1092,10 +1058,10 @@
           <t xml:space="preserve">　調整交付金見込交付割合を5.533％→5.522％に</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="6" t="n">
         <v>6047.579154673352</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="7" t="n">
         <v>2.850073742210952</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1110,10 +1076,10 @@
           <t xml:space="preserve">　補正後被保険者数を10,245人→10,235人に</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="6" t="n">
         <v>6053.502830038761</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>5.923675365409508</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1128,10 +1094,10 @@
           <t xml:space="preserve">　地域支援事業費をシステムの額に</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>6053.502273872105</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="7" t="n">
         <v>-0.0005561666557696299</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1146,10 +1112,10 @@
           <t xml:space="preserve">　標準給付費をシステムの額に</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>6533.45567558078</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>479.9534017086744</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1164,10 +1130,10 @@
           <t>システムの値</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>6533.46</v>
       </c>
-      <c r="C8" s="8" t="n"/>
+      <c r="C8" s="7" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ワークシートの表示値</t>
@@ -1214,16 +1180,16 @@
           <t>在宅サービス</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <v>409239</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>523408</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>114169</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="9" t="n">
         <v>1.278978787456718</v>
       </c>
     </row>
@@ -1233,16 +1199,16 @@
           <t>居住系サービス</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="6" t="n">
         <v>140627</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>144729</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>4102</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <v>1.029169362924616</v>
       </c>
     </row>
@@ -1252,16 +1218,16 @@
           <t>施設サービス</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="6" t="n">
         <v>410829</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>387688</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>-23141</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>0.9436724281878835</v>
       </c>
     </row>
@@ -1271,16 +1237,16 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="6" t="n">
         <v>960695</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>1055825</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>95130</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="10" t="n">
         <v>1.099022062152921</v>
       </c>
     </row>
@@ -1342,7 +1308,7 @@
           <t>3,354,617千円</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>＋260,669千円（＋8.4％）</t>
         </is>
@@ -1364,7 +1330,7 @@
           <t>3,142,496千円</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>＋272,560千円（＋9.5％）</t>
         </is>
@@ -1386,7 +1352,7 @@
           <t>191,749千円</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -1408,7 +1374,7 @@
           <t>103,743千円</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -1430,7 +1396,7 @@
           <t>10,275人</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>差9人</t>
         </is>
@@ -1452,7 +1418,7 @@
           <t>10,235人</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>当方の標準割合でシステムの値を再現</t>
         </is>
@@ -1474,7 +1440,7 @@
           <t>標準給付費＋地域支援事業費</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -1496,7 +1462,7 @@
           <t>標準給付費＋総合事業費</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -1518,9 +1484,9 @@
           <t>標準給付費＋総合事業費</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>訂正して一致</t>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1506,7 @@
           <t>5.522％</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>差0.011ポイント</t>
         </is>
@@ -1562,7 +1528,7 @@
           <t>99.40％</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>差0.05ポイント</t>
         </is>
@@ -1584,7 +1550,7 @@
           <t>0円</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>一致。政策判断が要る</t>
         </is>
@@ -1606,7 +1572,7 @@
           <t>6,533円</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>+485円</t>
         </is>
@@ -1660,10 +1626,10 @@
           <t>総給付費</t>
         </is>
       </c>
-      <c r="B2" s="14" t="n">
+      <c r="B2" s="13" t="n">
         <v>5772.56</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="14" t="n">
         <v>0.8835</v>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
@@ -1674,10 +1640,10 @@
           <t xml:space="preserve">　在宅サービス</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>2849.84</v>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="14" t="n">
         <v>0.4362</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1692,10 +1658,10 @@
           <t xml:space="preserve">　居住系サービス</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="13" t="n">
         <v>786.24</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.1203</v>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -1706,10 +1672,10 @@
           <t xml:space="preserve">　施設サービス</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>2136.47</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="14" t="n">
         <v>0.327</v>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -1720,10 +1686,10 @@
           <t>その他給付費</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>399.64</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="14" t="n">
         <v>0.0612</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1738,10 +1704,10 @@
           <t>地域支援事業費</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="13" t="n">
         <v>361.26</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>0.0553</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1756,10 +1722,10 @@
           <t>財政安定化基金</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="15" t="n"/>
+      <c r="C8" s="14" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>拠出金・償還金とも0</t>
@@ -1772,10 +1738,10 @@
           <t>市町村特別給付費等</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="15" t="n"/>
+      <c r="C9" s="14" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>実施なし</t>
@@ -1788,10 +1754,10 @@
           <t>保険料収納必要額（月額）</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>6533.46</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr"/>
@@ -1802,10 +1768,10 @@
           <t xml:space="preserve">　準備基金取崩額</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="15" t="n"/>
+      <c r="C11" s="14" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>未入力。政策判断が要る</t>
@@ -1818,10 +1784,10 @@
           <t>基準保険料額（月額）</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>6533.46</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1843,96 +1809,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>見つかったこと</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>調整交付金見込額の基数に総合事業費を含めていませんでした。当方は標準給付費のみを基数としていましたが、システムは調整交付金相当額（5％）と同じく（標準給付費＋総合事業費）を基数としています</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>確かめ方①</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>ワークシート「5_保険料推計」94行の調整交付金見込額（令和9年度70,959千円）を、97行の見込交付割合6.11％で割り戻すと1,161,354千円になります。これは標準給付費1,126,772千円＋総合事業費34,581千円と1円まで一致します。令和10・11年度も同じです</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>確かめ方②</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>第9期計画の実数で検算しました。第9期の標準給付費3,566,486千円・地域支援事業費207,260千円・総合事業費110,960千円を入れると月額6,865円となり、第9期計画の算定値6,886円（基金取崩前）との差は0.3％です。訂正前の算式では6,442円で、差は6.4％ありました</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>影響</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>当方の算定は6,095円ではなく6,048円になります（▲47円）。100円未満を切り上げた6,100円は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>直したところ</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>算定スクリプトの保険料算式（build_ono_tanka.premium）を訂正し、これを用いている成果物をすべて作り直しました</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2044,7 +1920,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>6,533円と6,095円のどちらを計画に載せるかをお諮りします。据え置きか引下げかの分かれ目にあたります</t>
+          <t>6,533円と6,048円のどちらを計画に載せるかをお諮りします。据え置きか引下げかの分かれ目にあたります</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_システムとの突合_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_システムとの突合_20260928.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>残るワーニング33件はすべて「小野町に利用がないサービスが0」。直す必要なし</t>
+          <t>残るワーニング33件は、直近年度の実績が0の要介護度区分が0のまま延びたもの。直す必要なし</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>小野町に提供事業所がない</t>
+          <t>令和6・7年度の実績が0（令和5年度に介護給付1件があるのみ）</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>令和6・7年度の実績が0（令和3年度14件→令和4年度10件→令和5年度1件と減って0になった）</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>この2区分の利用がない</t>
+          <t>この2区分の実績が0。サービス全体では令和7年度に115件の実績がある</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_システムとの突合_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_システムとの突合_20260928.xlsx
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>政策判断です。年報 様式4 の保有額は12,000千円ですが、令和4年度末の120,000千円から1桁減っており、基金運用状況調書での確認をお願いしています</t>
+          <t>政策判断です。残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円です。令和7年度末の残高（財産に関する調書）の確認をお願いしています</t>
         </is>
       </c>
     </row>
